--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +706,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,10 +744,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -756,39 +754,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -860,12 +856,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,10 +894,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -910,39 +904,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1014,12 +1006,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1091,12 +1083,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1168,12 +1160,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1245,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1322,12 +1314,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1352,7 +1344,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1360,8 +1352,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1370,37 +1364,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1472,12 +1468,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1549,12 +1545,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1626,12 +1622,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1703,12 +1699,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1780,12 +1776,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1810,7 +1806,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1818,10 +1814,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1830,39 +1824,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1934,12 +1926,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2011,12 +2003,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2041,7 +2033,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2049,8 +2041,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2059,37 +2053,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2161,12 +2157,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2191,7 +2187,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2199,47 +2195,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2349,8 +2349,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2359,37 +2361,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2422,8 +2426,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2432,37 +2438,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2487,7 +2495,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2495,10 +2503,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2507,39 +2513,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2564,7 +2568,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2572,8 +2576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2582,37 +2588,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2648,9 +2656,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2680,12 +2688,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2757,12 +2765,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2796,7 +2804,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2830,12 +2838,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2860,7 +2868,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2868,10 +2876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2880,39 +2886,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2984,12 +2988,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3014,7 +3018,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3022,10 +3026,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3034,39 +3036,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3099,10 +3099,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3111,39 +3109,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3215,12 +3211,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3245,7 +3241,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3253,10 +3249,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3265,39 +3259,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3369,12 +3361,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3446,12 +3438,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3523,12 +3515,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3600,12 +3592,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3630,7 +3622,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3638,8 +3630,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3648,37 +3642,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3703,7 +3699,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3711,8 +3707,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3721,37 +3719,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3861,8 +3861,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3871,37 +3873,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3926,7 +3930,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3934,8 +3938,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3944,37 +3950,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3999,7 +4007,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4007,8 +4015,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4017,37 +4027,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4072,7 +4084,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4080,10 +4092,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4092,39 +4102,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4149,7 +4157,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4157,10 +4165,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4169,39 +4175,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4273,12 +4277,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4303,7 +4307,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4311,10 +4315,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4323,39 +4325,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4388,10 +4388,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4400,39 +4398,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4457,7 +4453,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4465,10 +4461,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4477,39 +4471,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4581,12 +4573,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4658,12 +4650,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4735,12 +4727,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4812,12 +4804,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4889,12 +4881,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4966,12 +4958,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5043,12 +5035,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5073,7 +5065,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5081,8 +5073,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5091,37 +5085,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5146,7 +5142,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5154,8 +5150,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5164,37 +5162,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5227,47 +5227,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5292,7 +5296,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5300,8 +5304,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5310,37 +5316,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5365,7 +5373,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5373,8 +5381,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>1</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5383,37 +5393,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5438,7 +5450,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5446,8 +5458,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5456,37 +5470,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5511,7 +5527,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5519,10 +5535,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5531,39 +5545,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5599,9 +5611,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5631,12 +5643,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5661,7 +5673,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5669,51 +5681,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5747,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5781,12 +5789,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5811,7 +5819,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5819,10 +5827,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5831,39 +5837,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5888,7 +5892,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5896,10 +5900,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5908,39 +5910,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6050,51 +6050,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6166,12 +6162,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6196,7 +6192,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6204,10 +6200,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6216,109 +6210,569 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,14 +706,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -736,7 +736,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,8 +744,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -754,37 +756,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -856,12 +860,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -929,12 +933,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1006,14 +1010,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1044,10 +1048,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1056,39 +1058,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1622,12 +1622,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1776,14 +1776,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1814,8 +1814,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1824,37 +1826,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1926,14 +1930,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1956,7 +1960,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1964,10 +1968,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1976,39 +1978,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2080,12 +2080,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2157,12 +2157,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2465,14 +2465,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2503,8 +2503,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2513,37 +2515,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2615,12 +2619,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2656,9 +2660,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2688,12 +2692,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2765,14 +2769,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2804,11 +2808,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2838,14 +2842,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2868,7 +2872,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2876,8 +2880,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2886,39 +2892,41 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2941,7 +2949,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2949,10 +2957,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2961,39 +2967,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3061,14 +3065,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3091,7 +3095,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3099,8 +3103,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3109,39 +3115,41 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3164,7 +3172,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3172,10 +3180,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3184,39 +3190,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3284,12 +3288,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3361,14 +3365,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3391,7 +3395,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3399,10 +3403,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3411,39 +3413,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3900,12 +3900,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4054,14 +4054,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4092,8 +4092,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4102,39 +4104,41 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4157,7 +4161,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4165,8 +4169,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4175,39 +4181,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4230,7 +4238,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4238,10 +4246,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4250,39 +4256,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4350,14 +4354,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4388,8 +4392,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4398,37 +4404,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4496,14 +4504,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4526,7 +4534,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4534,10 +4542,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4546,41 +4552,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4611,10 +4615,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4623,39 +4625,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5497,14 +5497,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5535,8 +5535,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5545,39 +5547,41 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5600,7 +5604,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5608,8 +5612,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5618,37 +5624,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5684,9 +5692,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5716,12 +5724,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5789,14 +5797,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5828,11 +5836,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5862,12 +5870,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5935,14 +5943,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5965,7 +5973,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5973,10 +5981,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5985,39 +5991,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6053,9 +6057,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6085,12 +6089,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6162,14 +6166,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6201,11 +6205,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6235,12 +6239,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6312,14 +6316,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6342,7 +6346,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6350,10 +6354,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6362,39 +6364,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6466,12 +6466,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6697,82 +6697,236 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,51 +590,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -659,7 +655,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -667,10 +663,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -679,39 +673,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -736,7 +728,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,10 +736,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -756,39 +746,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -813,7 +801,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -821,51 +809,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +874,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,8 +882,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -908,37 +894,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +951,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -971,10 +959,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -983,39 +969,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1040,7 +1024,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,8 +1032,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1058,37 +1044,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1160,12 +1148,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1237,12 +1225,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1314,12 +1302,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1344,7 +1332,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1352,10 +1340,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1364,39 +1350,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1452,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,7 +1482,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1506,10 +1490,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1518,39 +1500,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1622,12 +1602,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1699,12 +1679,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1776,12 +1756,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1853,12 +1833,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1930,12 +1910,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1960,7 +1940,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1968,8 +1948,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1978,37 +1960,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2080,12 +2064,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2157,12 +2141,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2234,12 +2218,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2311,12 +2295,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2388,12 +2372,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2418,7 +2402,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2426,10 +2410,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2438,39 +2420,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2542,12 +2522,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2619,12 +2599,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2649,7 +2629,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2657,8 +2637,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2667,37 +2649,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2769,12 +2753,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2799,7 +2783,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2807,47 +2791,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2919,12 +2907,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2949,7 +2937,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2957,8 +2945,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>1</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2967,37 +2957,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3022,7 +3014,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3030,8 +3022,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3040,37 +3034,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3095,7 +3091,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3103,10 +3099,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3115,39 +3109,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3172,7 +3164,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3180,8 +3172,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3190,37 +3184,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3256,9 +3252,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3288,12 +3284,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3365,12 +3361,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3404,7 +3400,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3438,12 +3434,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3468,7 +3464,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3476,10 +3472,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3488,39 +3482,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3592,12 +3584,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3622,7 +3614,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3630,10 +3622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3642,39 +3632,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3699,7 +3687,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3707,10 +3695,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3719,39 +3705,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3823,12 +3807,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3853,7 +3837,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3861,10 +3845,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3873,39 +3855,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3977,12 +3957,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4054,12 +4034,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4131,12 +4111,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4208,12 +4188,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4238,7 +4218,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4246,8 +4226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4256,37 +4238,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4311,7 +4295,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4319,8 +4303,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4329,37 +4315,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4431,12 +4419,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4461,7 +4449,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4469,8 +4457,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4479,37 +4469,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4534,7 +4526,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4542,8 +4534,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4552,37 +4546,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4607,7 +4603,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4615,8 +4611,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4625,37 +4623,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4688,10 +4688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4700,39 +4698,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4757,7 +4753,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4765,10 +4761,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4777,39 +4771,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4881,12 +4873,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4911,7 +4903,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4919,10 +4911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4931,39 +4921,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4988,7 +4976,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4996,10 +4984,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5008,39 +4994,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5065,7 +5049,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5073,10 +5057,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5085,39 +5067,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5189,12 +5169,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5266,12 +5246,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5343,12 +5323,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5420,12 +5400,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5497,12 +5477,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5574,12 +5554,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5651,12 +5631,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5681,7 +5661,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5689,8 +5669,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5699,37 +5681,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5754,7 +5738,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5762,8 +5746,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5772,37 +5758,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5827,7 +5815,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5835,47 +5823,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5900,7 +5892,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5908,8 +5900,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5918,37 +5912,39 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5973,7 +5969,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5981,8 +5977,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>1</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5991,37 +5989,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6054,8 +6054,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6064,37 +6066,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6119,7 +6123,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6127,10 +6131,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6139,39 +6141,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6207,9 +6207,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6277,51 +6277,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6355,7 +6351,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6389,12 +6385,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6419,7 +6415,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6427,10 +6423,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6439,39 +6433,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6496,7 +6488,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6504,10 +6496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6516,39 +6506,37 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6620,12 +6608,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6650,7 +6638,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6658,51 +6646,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6774,12 +6758,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6804,7 +6788,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6812,10 +6796,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6824,109 +6806,569 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,47 +590,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -655,7 +659,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -663,8 +667,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -673,37 +679,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -728,7 +736,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -736,8 +744,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -746,37 +756,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -801,7 +813,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -809,47 +821,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -874,7 +890,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -882,10 +898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -894,39 +908,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -951,7 +963,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -959,8 +971,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -969,37 +983,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1024,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1032,51 +1048,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1101,7 +1113,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,10 +1121,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1121,39 +1131,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1178,7 +1186,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1186,10 +1194,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1198,39 +1204,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1263,51 +1267,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1340,8 +1340,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1350,37 +1352,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,7 +1409,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1413,10 +1417,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1425,39 +1427,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1490,8 +1490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1500,37 +1502,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1602,12 +1606,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1679,12 +1683,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1756,12 +1760,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1794,10 +1798,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1806,39 +1808,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1948,10 +1948,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1960,39 +1958,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2064,12 +2060,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2141,12 +2137,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2218,12 +2214,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2295,12 +2291,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2372,12 +2368,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2402,7 +2398,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2410,8 +2406,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2420,37 +2418,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2868,10 +2868,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2880,39 +2878,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2984,12 +2980,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3061,12 +3057,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3091,7 +3087,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3099,8 +3095,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3109,37 +3107,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3249,47 +3249,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3361,12 +3365,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3391,7 +3395,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3399,8 +3403,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3409,37 +3415,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3464,7 +3472,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3472,8 +3480,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3482,37 +3492,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3537,7 +3549,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3545,10 +3557,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3557,39 +3567,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3614,7 +3622,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3622,8 +3630,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3632,37 +3642,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3698,9 +3710,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3730,12 +3742,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3807,12 +3819,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3846,7 +3858,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3892,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3910,7 +3922,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3918,10 +3930,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3930,39 +3940,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4034,12 +4042,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4064,7 +4072,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4072,10 +4080,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4084,39 +4090,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4141,7 +4145,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4149,10 +4153,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4161,39 +4163,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4303,10 +4303,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4315,39 +4313,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4419,12 +4415,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4496,12 +4492,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4573,12 +4569,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4650,12 +4646,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4680,7 +4676,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4688,8 +4684,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4698,37 +4696,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4761,8 +4761,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4771,37 +4773,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4873,12 +4877,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4903,7 +4907,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4911,8 +4915,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4921,37 +4927,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4976,7 +4984,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4984,8 +4992,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4994,37 +5004,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5049,7 +5061,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5057,8 +5069,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5067,37 +5081,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5122,7 +5138,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5130,10 +5146,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5142,39 +5156,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5199,7 +5211,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5207,10 +5219,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5219,39 +5229,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5323,12 +5331,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5353,7 +5361,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5361,10 +5369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5373,39 +5379,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5430,7 +5434,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5438,10 +5442,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5450,39 +5452,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5515,10 +5515,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5527,39 +5525,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5631,12 +5627,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5708,12 +5704,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5785,12 +5781,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5862,12 +5858,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5939,12 +5935,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,12 +6012,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6093,12 +6089,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6123,7 +6119,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6131,8 +6127,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6141,37 +6139,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6204,8 +6204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6214,37 +6216,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6269,7 +6273,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6277,47 +6281,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6342,7 +6350,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6350,8 +6358,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6360,37 +6370,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6415,7 +6427,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6423,8 +6435,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>1</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6433,37 +6447,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6488,7 +6504,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6496,8 +6512,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6506,37 +6524,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6561,7 +6581,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6569,10 +6589,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6581,39 +6599,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6649,9 +6665,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6681,12 +6697,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6711,7 +6727,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6719,51 +6735,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6797,7 +6809,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6831,12 +6843,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6861,7 +6873,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6869,10 +6881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6881,39 +6891,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6938,7 +6946,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6946,10 +6954,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6958,39 +6964,37 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7062,12 +7066,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7092,7 +7096,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7100,51 +7104,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7254,10 +7254,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7266,109 +7264,569 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +706,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -860,14 +860,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -890,7 +890,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,8 +898,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -908,37 +910,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1010,12 +1014,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1051,9 +1055,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1083,14 +1087,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1121,8 +1125,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1131,39 +1137,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1195,11 +1203,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1229,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1270,9 +1278,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1302,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1332,7 +1340,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1340,10 +1348,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1352,41 +1358,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1418,11 +1422,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1452,12 +1456,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1529,14 +1533,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1559,7 +1563,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1567,10 +1571,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1579,39 +1581,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1683,12 +1683,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1760,14 +1760,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1798,8 +1798,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1808,37 +1810,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1910,12 +1914,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1983,12 +1987,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2060,14 +2064,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2090,7 +2094,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2098,10 +2102,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2110,39 +2112,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2868,8 +2868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2878,37 +2880,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2980,14 +2984,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3010,7 +3014,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3018,10 +3022,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3030,39 +3032,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3519,14 +3519,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3557,8 +3557,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3567,37 +3569,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3669,12 +3673,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3710,9 +3714,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3742,12 +3746,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3819,14 +3823,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3858,11 +3862,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3892,14 +3896,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3922,7 +3926,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3930,8 +3934,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3940,39 +3946,41 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3995,7 +4003,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4003,10 +4011,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4015,39 +4021,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4115,14 +4119,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4145,7 +4149,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4153,8 +4157,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4163,39 +4169,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4218,7 +4226,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4226,10 +4234,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4238,39 +4244,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4338,12 +4342,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4415,14 +4419,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4453,10 +4457,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4465,39 +4467,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5108,14 +5108,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5146,8 +5146,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5156,39 +5158,41 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5211,7 +5215,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5219,8 +5223,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5229,39 +5235,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5284,7 +5292,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5292,10 +5300,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5304,39 +5310,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5404,14 +5408,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5434,7 +5438,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5442,8 +5446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5452,37 +5458,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5550,14 +5558,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5580,7 +5588,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5588,10 +5596,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5600,41 +5606,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5657,7 +5661,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5665,10 +5669,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5677,39 +5679,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6551,14 +6551,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6589,8 +6589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6599,39 +6601,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6654,7 +6658,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6662,8 +6666,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6672,37 +6678,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6738,9 +6746,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6770,12 +6778,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6843,14 +6851,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6882,11 +6890,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6916,12 +6924,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6989,14 +6997,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7019,7 +7027,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7027,10 +7035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7039,39 +7045,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7107,9 +7111,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7139,12 +7143,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7216,14 +7220,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7255,11 +7259,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7289,12 +7293,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7366,14 +7370,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7396,7 +7400,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7404,10 +7408,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7416,39 +7418,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7520,12 +7520,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7751,82 +7751,236 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,10 +590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -602,39 +600,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +702,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -783,12 +779,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -860,12 +856,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -937,12 +933,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1014,12 +1010,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1052,8 +1048,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1062,37 +1060,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1202,47 +1202,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1267,7 +1271,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1275,8 +1279,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1285,37 +1291,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1349,7 +1357,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1383,12 +1391,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1413,7 +1421,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1421,47 +1429,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1486,7 +1498,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1494,51 +1506,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1572,7 +1580,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1606,12 +1614,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1636,7 +1644,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1644,10 +1652,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1656,39 +1662,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1713,7 +1717,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1721,51 +1725,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1875,10 +1875,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1887,39 +1885,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1944,7 +1940,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1952,8 +1948,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1962,37 +1960,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2102,8 +2102,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2112,37 +2114,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2214,12 +2218,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2244,7 +2248,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2252,10 +2256,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2264,39 +2266,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2406,10 +2406,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2418,39 +2416,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2522,12 +2518,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2599,12 +2595,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2676,12 +2672,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2753,12 +2749,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2830,12 +2826,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2907,12 +2903,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2984,12 +2980,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3014,7 +3010,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3022,8 +3018,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3032,37 +3030,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3326,10 +3326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3338,39 +3336,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3442,12 +3438,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3519,12 +3515,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3596,12 +3592,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3673,12 +3669,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3703,7 +3699,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3711,8 +3707,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3721,37 +3719,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3861,47 +3861,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3973,12 +3977,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4012,7 +4016,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4046,12 +4050,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4076,7 +4080,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4084,8 +4088,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4094,37 +4100,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4149,7 +4157,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4157,51 +4165,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4226,7 +4230,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4234,8 +4238,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4244,37 +4250,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4308,7 +4316,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4342,12 +4350,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4372,7 +4380,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4380,10 +4388,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4392,39 +4398,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4449,7 +4453,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4457,8 +4461,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4467,37 +4473,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4522,7 +4530,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4530,10 +4538,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4542,39 +4548,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4599,7 +4603,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4607,10 +4611,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4619,39 +4621,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4761,10 +4761,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4773,39 +4771,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4877,12 +4873,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4954,12 +4950,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5031,12 +5027,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5108,12 +5104,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5185,12 +5181,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5262,12 +5258,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5292,7 +5288,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5300,8 +5296,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5310,37 +5308,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5373,8 +5373,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5383,37 +5385,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5485,12 +5489,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5515,7 +5519,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5523,8 +5527,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5533,37 +5539,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5631,12 +5639,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5704,12 +5712,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5781,12 +5789,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5811,7 +5819,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5819,10 +5827,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5831,39 +5837,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5888,7 +5892,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5896,10 +5900,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5908,39 +5910,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5973,10 +5973,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5985,39 +5983,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6089,12 +6085,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6166,12 +6162,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6243,12 +6239,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6320,12 +6316,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6397,12 +6393,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6474,12 +6470,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6551,12 +6547,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6628,12 +6624,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6705,12 +6701,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6735,7 +6731,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6743,8 +6739,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6753,37 +6751,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6816,8 +6816,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6826,37 +6828,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6881,7 +6885,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6889,47 +6893,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6954,7 +6962,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6962,8 +6970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6972,37 +6982,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7036,7 +7048,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7070,12 +7082,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7143,12 +7155,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7173,7 +7185,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7181,51 +7193,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7261,9 +7269,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7293,12 +7301,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7323,7 +7331,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7331,10 +7339,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7343,39 +7349,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7409,7 +7413,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7443,12 +7447,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7520,12 +7524,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7550,7 +7554,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7558,51 +7562,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7712,10 +7712,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7724,39 +7722,37 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7828,12 +7824,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7905,82 +7901,390 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,8 +590,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -600,37 +602,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -702,12 +706,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -779,12 +783,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -856,12 +860,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -933,12 +937,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1010,12 +1014,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1087,12 +1091,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1164,12 +1168,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1241,12 +1245,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1318,12 +1322,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,7 +1352,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1356,8 +1360,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1366,37 +1372,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1476,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1509,9 +1517,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1541,12 +1549,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1571,7 +1579,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1579,8 +1587,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1589,37 +1599,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1653,7 +1665,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1687,12 +1699,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1717,7 +1729,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1725,47 +1737,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1837,12 +1853,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1867,7 +1883,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1875,8 +1891,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1885,37 +1903,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1987,12 +2007,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2064,12 +2084,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2094,7 +2114,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2102,10 +2122,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2114,39 +2132,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2218,12 +2234,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2259,9 +2275,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2291,12 +2307,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2368,12 +2384,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2407,7 +2423,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2441,12 +2457,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2518,12 +2534,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2595,12 +2611,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2672,12 +2688,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2749,12 +2765,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2826,12 +2842,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2903,12 +2919,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2980,12 +2996,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3057,12 +3073,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3134,12 +3150,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3164,7 +3180,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3172,10 +3188,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3184,39 +3198,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3288,12 +3300,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3329,9 +3341,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3361,12 +3373,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3391,7 +3403,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3399,10 +3411,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3411,39 +3421,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3468,7 +3476,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3476,10 +3484,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3488,39 +3494,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3545,7 +3549,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3553,51 +3557,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3707,10 +3707,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3719,39 +3717,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3823,12 +3819,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3900,12 +3896,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3977,12 +3973,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4007,7 +4003,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4015,8 +4011,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4025,37 +4023,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4088,10 +4088,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4100,39 +4098,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4157,7 +4153,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4165,47 +4161,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4238,10 +4238,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4250,39 +4248,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4307,7 +4303,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4315,8 +4311,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>1</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4325,37 +4323,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4388,8 +4388,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4398,37 +4400,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4500,12 +4504,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4530,7 +4534,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4538,8 +4542,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4548,37 +4554,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4603,7 +4611,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4611,8 +4619,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4621,37 +4631,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4723,12 +4735,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4753,7 +4765,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4761,8 +4773,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4771,37 +4785,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4873,12 +4889,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4950,12 +4966,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5027,12 +5043,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5104,12 +5120,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5134,7 +5150,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5142,10 +5158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5154,39 +5168,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5258,12 +5270,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5335,12 +5347,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5412,12 +5424,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5489,12 +5501,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5566,12 +5578,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5596,7 +5608,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5604,8 +5616,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5614,37 +5628,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5669,7 +5685,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5677,8 +5693,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5687,37 +5705,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5789,12 +5809,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5862,12 +5882,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5892,7 +5912,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5900,8 +5920,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5910,37 +5932,39 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5976,9 +6000,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -6008,12 +6032,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6085,12 +6109,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6115,7 +6139,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6123,10 +6147,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6135,39 +6157,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6192,7 +6212,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6200,10 +6220,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6212,39 +6230,37 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6316,12 +6332,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6346,7 +6362,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6354,10 +6370,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6366,39 +6380,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6423,7 +6435,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6431,10 +6443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6443,39 +6453,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6547,12 +6555,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6577,7 +6585,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6585,10 +6593,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6597,39 +6603,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6701,12 +6705,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6778,12 +6782,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6855,12 +6859,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6932,12 +6936,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7009,12 +7013,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7047,8 +7051,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7057,37 +7063,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7112,7 +7120,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7120,8 +7128,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7130,37 +7140,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7185,7 +7197,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7193,47 +7205,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7258,7 +7274,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7266,8 +7282,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7276,37 +7294,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7331,7 +7351,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7339,8 +7359,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>1</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7349,37 +7371,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7447,12 +7471,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7477,7 +7501,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7485,10 +7509,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7497,39 +7519,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7554,7 +7574,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7562,47 +7582,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7627,7 +7651,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7635,10 +7659,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7647,39 +7669,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7713,7 +7733,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7747,12 +7767,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7777,7 +7797,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7785,10 +7805,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7797,39 +7815,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7901,12 +7917,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7978,12 +7994,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8055,12 +8071,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8132,12 +8148,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8209,82 +8225,1898 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,10 +590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -602,39 +600,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +702,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -783,12 +779,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -860,12 +856,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -937,12 +933,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1014,12 +1010,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1052,10 +1048,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1064,39 +1058,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1168,12 +1160,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,7 +1190,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1206,51 +1198,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1322,12 +1310,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1352,59 +1340,55 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1429,7 +1413,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1437,10 +1421,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1449,39 +1431,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1506,7 +1486,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1515,7 +1495,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1524,15 +1504,15 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1549,12 +1529,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1579,7 +1559,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1587,51 +1567,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1664,8 +1640,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1674,37 +1652,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1729,7 +1709,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1737,10 +1717,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1749,39 +1727,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1806,7 +1782,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1814,10 +1790,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1826,39 +1800,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1930,12 +1902,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1960,7 +1932,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1968,51 +1940,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2084,12 +2052,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2123,7 +2091,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2157,12 +2125,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2234,12 +2202,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2307,12 +2275,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2384,12 +2352,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2457,12 +2425,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2534,12 +2502,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2611,12 +2579,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2688,12 +2656,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2718,7 +2686,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2726,10 +2694,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2738,39 +2704,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2842,12 +2806,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2919,12 +2883,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2996,12 +2960,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3073,12 +3037,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3150,12 +3114,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3180,7 +3144,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3188,8 +3152,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3198,37 +3164,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3300,12 +3268,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3330,7 +3298,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3338,47 +3306,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3403,7 +3375,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3411,8 +3383,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3421,37 +3395,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3476,7 +3452,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3484,8 +3460,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3494,37 +3472,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3560,9 +3540,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3592,12 +3572,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3669,12 +3649,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3699,7 +3679,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3707,8 +3687,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3717,37 +3699,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3819,12 +3803,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3896,12 +3880,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3973,12 +3957,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4050,12 +4034,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4080,7 +4064,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4088,8 +4072,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4098,37 +4084,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4200,12 +4188,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4230,7 +4218,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4238,8 +4226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4248,37 +4238,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4350,12 +4342,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4427,12 +4419,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4504,12 +4496,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4581,12 +4573,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4658,12 +4650,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4688,7 +4680,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4696,10 +4688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4708,39 +4698,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4812,12 +4800,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4842,7 +4830,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4850,10 +4838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4862,39 +4848,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4966,12 +4950,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5043,12 +5027,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5120,12 +5104,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5150,7 +5134,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5158,8 +5142,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5168,37 +5154,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5270,12 +5258,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5300,7 +5288,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5308,10 +5296,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5320,39 +5306,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5424,12 +5408,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5454,7 +5438,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5462,51 +5446,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5578,12 +5558,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5608,7 +5588,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5616,10 +5596,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5628,39 +5606,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5732,12 +5708,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5809,12 +5785,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5839,7 +5815,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5847,8 +5823,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5857,37 +5835,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5959,12 +5939,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5989,7 +5969,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5997,47 +5977,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6109,12 +6093,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6139,7 +6123,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6147,8 +6131,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6157,37 +6143,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6212,7 +6200,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6220,8 +6208,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6230,37 +6220,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6332,12 +6324,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6405,12 +6397,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6435,7 +6427,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6443,8 +6435,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6453,37 +6447,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6508,7 +6504,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6516,51 +6512,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6628,12 +6620,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6658,7 +6650,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6666,10 +6658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6678,39 +6668,37 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6735,7 +6723,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6743,51 +6731,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6859,12 +6843,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6889,7 +6873,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6897,10 +6881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6909,39 +6891,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7013,12 +6993,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7090,12 +7070,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7167,12 +7147,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7244,12 +7224,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7274,7 +7254,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7282,10 +7262,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7294,39 +7272,37 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7398,12 +7374,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7471,12 +7447,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7501,7 +7477,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7509,8 +7485,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7519,37 +7497,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7621,12 +7601,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7651,7 +7631,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7659,8 +7639,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7669,37 +7651,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7724,7 +7708,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7732,8 +7716,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7742,37 +7728,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7797,7 +7785,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7805,8 +7793,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7815,37 +7805,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7917,12 +7909,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7994,12 +7986,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8071,12 +8063,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8148,12 +8140,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8225,12 +8217,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8302,12 +8294,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8332,7 +8324,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8340,10 +8332,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8352,39 +8342,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8456,12 +8444,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8533,12 +8521,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8610,12 +8598,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8687,12 +8675,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8764,12 +8752,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8841,12 +8829,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8871,7 +8859,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8879,8 +8867,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8889,37 +8879,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8944,7 +8936,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8952,8 +8944,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8962,37 +8956,39 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9028,9 +9024,9 @@
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -9060,12 +9056,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9090,7 +9086,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9098,8 +9094,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -9108,37 +9106,39 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9172,11 +9172,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9206,12 +9206,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9244,8 +9244,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9254,37 +9256,39 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9309,7 +9313,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9317,10 +9321,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9329,39 +9331,37 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9397,9 +9397,9 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9429,12 +9429,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9579,12 +9579,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9617,10 +9617,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9629,39 +9627,37 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9733,12 +9729,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9763,7 +9759,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9771,10 +9767,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9783,39 +9777,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9887,12 +9879,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9964,12 +9956,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10041,82 +10033,3264 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,14 +552,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,8 +590,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -600,37 +602,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -702,14 +706,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -732,7 +736,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,10 +744,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -752,39 +754,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1010,14 +1010,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,8 +1048,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1058,37 +1060,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1160,12 +1164,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1201,9 +1205,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1233,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1310,14 +1314,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1343,17 +1347,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1383,14 +1387,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1413,7 +1417,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1421,8 +1425,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1431,39 +1437,41 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1486,33 +1494,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1529,12 +1537,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1570,9 +1578,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1602,14 +1610,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1632,7 +1640,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1640,10 +1648,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1652,41 +1658,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1718,11 +1722,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1752,14 +1756,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1782,7 +1786,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1790,8 +1794,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1800,39 +1806,41 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1855,7 +1863,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1863,10 +1871,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1875,39 +1881,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1943,9 +1947,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1975,12 +1979,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2052,14 +2056,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2091,11 +2095,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2125,12 +2129,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2202,14 +2206,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2241,11 +2245,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2275,12 +2279,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2352,14 +2356,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2391,11 +2395,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2425,12 +2429,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2502,14 +2506,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2540,10 +2544,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2552,39 +2554,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2656,14 +2656,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2694,8 +2694,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2704,37 +2706,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2806,14 +2810,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2836,7 +2840,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2844,10 +2848,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2856,39 +2858,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3499,14 +3499,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3537,8 +3537,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3547,37 +3549,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3649,14 +3653,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3679,7 +3683,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3687,10 +3691,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3699,39 +3701,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4650,14 +4650,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4688,8 +4688,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4698,37 +4700,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4800,12 +4804,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4873,12 +4877,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4950,14 +4954,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4980,7 +4984,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4988,10 +4992,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5000,39 +5002,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5258,14 +5258,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5296,8 +5296,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5306,37 +5308,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5408,12 +5412,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5449,9 +5453,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5481,12 +5485,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5558,14 +5562,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5597,11 +5601,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5631,12 +5635,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5708,14 +5712,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5738,7 +5742,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5746,10 +5750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5758,39 +5760,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6324,14 +6324,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6362,8 +6362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6372,37 +6374,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6474,12 +6478,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6515,9 +6519,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6547,14 +6551,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6577,7 +6581,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6585,8 +6589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6595,39 +6601,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6659,11 +6667,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6693,12 +6701,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6734,9 +6742,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6766,14 +6774,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6796,7 +6804,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6804,10 +6812,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6816,41 +6822,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6882,11 +6886,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6916,12 +6920,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6993,14 +6997,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7023,7 +7027,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7031,10 +7035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7043,39 +7045,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7224,14 +7224,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7262,8 +7262,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7272,37 +7274,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7374,12 +7378,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7447,12 +7451,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7524,14 +7528,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7554,7 +7558,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7562,10 +7566,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7574,39 +7576,37 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7832,12 +7832,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8294,14 +8294,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8332,8 +8332,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8342,37 +8344,39 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8444,14 +8448,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8474,7 +8478,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8482,10 +8486,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8494,39 +8496,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8983,14 +8983,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -9021,8 +9021,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
-        <v>0</v>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -9031,37 +9033,39 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9133,12 +9137,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9174,9 +9178,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9206,12 +9210,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9283,14 +9287,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9322,11 +9326,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9356,14 +9360,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9386,7 +9390,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9394,8 +9398,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9404,39 +9410,41 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9459,7 +9467,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9467,10 +9475,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9479,39 +9485,37 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9579,14 +9583,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9609,7 +9613,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9617,8 +9621,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9627,39 +9633,41 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9682,7 +9690,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9690,10 +9698,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9702,39 +9708,37 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9802,12 +9806,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9879,14 +9883,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9909,7 +9913,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9917,10 +9921,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9929,39 +9931,37 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10033,12 +10033,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10264,12 +10264,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10572,14 +10572,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10610,8 +10610,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="2" t="n">
-        <v>0</v>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10620,39 +10622,41 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10675,7 +10679,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10683,8 +10687,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10693,39 +10699,41 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10748,7 +10756,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10756,10 +10764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10768,39 +10774,37 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10868,14 +10872,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10898,7 +10902,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10906,8 +10910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10916,37 +10922,39 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11014,14 +11022,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11044,7 +11052,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11052,10 +11060,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11064,41 +11070,39 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11121,7 +11125,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11129,10 +11133,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11141,39 +11143,37 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11553,12 +11553,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11861,12 +11861,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12015,14 +12015,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -12053,8 +12053,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -12063,39 +12065,41 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12118,7 +12122,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -12126,8 +12130,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="2" t="n">
-        <v>0</v>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -12136,37 +12142,39 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12202,9 +12210,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12234,12 +12242,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12307,14 +12315,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12346,11 +12354,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12380,12 +12388,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12453,14 +12461,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12483,7 +12491,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12491,10 +12499,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12503,39 +12509,37 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12571,9 +12575,9 @@
       <c r="I160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12603,12 +12607,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12680,14 +12684,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12719,11 +12723,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12753,12 +12757,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12830,14 +12834,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12860,7 +12864,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12868,10 +12872,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12880,39 +12882,37 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12984,12 +12984,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13215,82 +13215,236 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,14 +706,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -736,7 +736,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,8 +744,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -754,37 +756,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -856,14 +860,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -886,7 +890,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -894,10 +898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -906,39 +908,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1010,12 +1010,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1164,14 +1164,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1202,8 +1202,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1212,37 +1214,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1314,12 +1318,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1355,9 +1359,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1387,12 +1391,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1464,14 +1468,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1497,17 +1501,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1537,14 +1541,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1575,8 +1579,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1585,39 +1591,41 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1640,33 +1648,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1683,12 +1691,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1724,9 +1732,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1756,14 +1764,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1786,7 +1794,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1794,10 +1802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1806,41 +1812,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1872,11 +1876,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1906,14 +1910,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1936,7 +1940,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1944,8 +1948,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1954,39 +1960,41 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2009,7 +2017,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2017,10 +2025,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2029,39 +2035,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2097,9 +2101,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2129,12 +2133,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2206,14 +2210,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2245,11 +2249,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2279,12 +2283,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2356,14 +2360,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2395,11 +2399,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2429,12 +2433,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2506,14 +2510,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2545,11 +2549,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2579,12 +2583,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2656,14 +2660,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2694,10 +2698,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2706,39 +2708,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2810,14 +2810,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2848,8 +2848,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2858,37 +2860,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2960,14 +2964,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2990,7 +2994,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2998,10 +3002,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3010,39 +3012,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3653,14 +3653,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3691,8 +3691,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3701,37 +3703,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3803,14 +3807,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3841,10 +3845,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3853,39 +3855,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4804,14 +4804,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4842,8 +4842,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4852,37 +4854,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4954,12 +4958,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5027,12 +5031,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5104,14 +5108,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5134,7 +5138,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5142,10 +5146,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5154,39 +5156,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5412,14 +5412,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5450,8 +5450,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5460,37 +5462,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5562,12 +5566,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5603,9 +5607,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5635,12 +5639,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5712,14 +5716,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5751,11 +5755,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5785,12 +5789,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5862,14 +5866,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5892,7 +5896,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5900,10 +5904,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5912,39 +5914,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6478,14 +6478,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6516,8 +6516,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6526,37 +6528,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6628,12 +6632,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6669,9 +6673,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6701,14 +6705,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6731,7 +6735,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6739,8 +6743,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6749,39 +6755,41 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6813,11 +6821,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6847,12 +6855,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6888,9 +6896,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6920,14 +6928,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6950,7 +6958,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6958,10 +6966,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6970,41 +6976,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7036,11 +7040,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7070,12 +7074,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7147,14 +7151,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7177,7 +7181,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7185,10 +7189,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7197,39 +7199,37 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7378,14 +7378,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7416,8 +7416,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7426,37 +7428,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7528,12 +7532,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7601,12 +7605,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7678,14 +7682,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7708,7 +7712,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7716,10 +7720,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7728,39 +7730,37 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7832,12 +7832,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8448,14 +8448,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8486,8 +8486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8496,37 +8498,39 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8598,14 +8602,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8628,7 +8632,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8636,10 +8640,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8648,39 +8650,37 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8829,12 +8829,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9060,12 +9060,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9137,14 +9137,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9175,8 +9175,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9185,37 +9187,39 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9287,12 +9291,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9328,9 +9332,9 @@
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9360,12 +9364,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9437,14 +9441,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9476,11 +9480,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9510,14 +9514,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9540,7 +9544,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9548,8 +9552,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9558,39 +9564,41 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9613,7 +9621,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9621,10 +9629,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9633,39 +9639,37 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9733,14 +9737,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9763,7 +9767,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9771,8 +9775,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9781,39 +9787,41 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9836,7 +9844,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9844,10 +9852,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9856,39 +9862,37 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9956,12 +9960,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10033,14 +10037,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10063,7 +10067,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -10071,10 +10075,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -10083,39 +10085,37 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10264,12 +10264,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10649,12 +10649,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10726,14 +10726,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10764,8 +10764,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="n">
-        <v>0</v>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10774,39 +10776,41 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10829,7 +10833,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10837,8 +10841,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10847,39 +10853,41 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10902,7 +10910,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10910,10 +10918,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10922,39 +10928,37 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11022,14 +11026,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11052,7 +11056,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11060,8 +11064,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11070,37 +11076,39 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11168,14 +11176,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11198,7 +11206,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11206,10 +11214,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -11218,41 +11224,39 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11275,7 +11279,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11283,10 +11287,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11295,39 +11297,37 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11553,12 +11553,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11861,12 +11861,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12092,12 +12092,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12169,14 +12169,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12207,8 +12207,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12217,39 +12219,41 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12272,7 +12276,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12280,8 +12284,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="2" t="n">
-        <v>0</v>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12290,37 +12296,39 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12356,9 +12364,9 @@
       <c r="I157" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12388,12 +12396,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12461,14 +12469,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12500,11 +12508,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12534,12 +12542,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12607,14 +12615,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12637,7 +12645,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12645,10 +12653,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12657,39 +12663,37 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12725,9 +12729,9 @@
       <c r="I162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12757,12 +12761,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12834,14 +12838,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12873,11 +12877,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12907,12 +12911,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12984,14 +12988,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -13014,7 +13018,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -13022,10 +13026,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I166" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -13034,39 +13036,37 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13215,12 +13215,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13292,12 +13292,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13369,82 +13369,236 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,14 +552,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,10 +590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -602,39 +600,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +702,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -783,12 +779,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -860,14 +856,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -890,7 +886,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,8 +894,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -908,37 +906,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1010,14 +1010,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,10 +1048,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1060,39 +1058,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1164,12 +1160,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1241,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1318,14 +1314,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1348,7 +1344,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1356,8 +1352,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1366,37 +1364,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1509,9 +1509,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1618,14 +1618,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1651,17 +1651,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1691,14 +1691,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1729,8 +1729,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1739,39 +1741,41 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1794,33 +1798,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1837,12 +1841,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1878,9 +1882,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1910,14 +1914,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -1940,7 +1944,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1948,10 +1952,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1960,41 +1962,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2026,11 +2026,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2060,14 +2060,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2098,8 +2098,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2108,39 +2110,41 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2163,7 +2167,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2171,10 +2175,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2183,39 +2185,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2251,9 +2251,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2360,14 +2360,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2399,11 +2399,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2510,14 +2510,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2549,11 +2549,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2660,14 +2660,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2699,11 +2699,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2810,14 +2810,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2848,10 +2848,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2860,39 +2858,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2964,14 +2960,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -2994,7 +2990,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3002,8 +2998,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3012,37 +3010,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3152,10 +3152,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3164,39 +3162,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3268,12 +3264,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3345,12 +3341,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3422,12 +3418,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3499,12 +3495,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3576,12 +3572,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3653,12 +3649,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3730,12 +3726,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3807,14 +3803,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3837,7 +3833,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3845,8 +3841,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3855,37 +3853,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3957,14 +3957,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3995,10 +3995,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4007,39 +4005,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4111,12 +4107,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4188,12 +4184,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4265,12 +4261,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4342,12 +4338,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4419,12 +4415,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4496,12 +4492,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4573,12 +4569,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4650,12 +4646,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4727,12 +4723,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4804,12 +4800,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4881,12 +4877,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4958,14 +4954,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -4988,7 +4984,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4996,8 +4992,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5006,37 +5004,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5258,14 +5258,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5296,10 +5296,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5308,39 +5306,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5412,12 +5408,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5489,12 +5485,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5566,14 +5562,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5596,7 +5592,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5604,8 +5600,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5614,37 +5612,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5757,9 +5757,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5866,14 +5866,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -5905,11 +5905,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,14 +6016,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6054,10 +6054,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6066,39 +6064,37 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6170,12 +6166,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6247,12 +6243,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6324,12 +6320,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6401,12 +6397,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6478,12 +6474,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6555,12 +6551,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6632,14 +6628,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6662,7 +6658,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6670,8 +6666,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6680,37 +6678,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6823,9 +6823,9 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6855,14 +6855,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6893,8 +6893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6903,39 +6905,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -6967,11 +6971,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -7001,12 +7005,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7042,9 +7046,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7074,14 +7078,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7104,7 +7108,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7112,10 +7116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7124,41 +7126,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7190,11 +7190,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7224,12 +7224,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7301,14 +7301,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7339,10 +7339,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7351,39 +7349,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7455,12 +7451,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7532,14 +7528,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7562,7 +7558,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7570,8 +7566,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7580,37 +7578,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7832,14 +7832,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7870,10 +7870,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7882,39 +7880,37 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7986,12 +7982,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8063,12 +8059,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8140,12 +8136,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8217,12 +8213,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8294,12 +8290,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8371,12 +8367,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8448,12 +8444,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8525,12 +8521,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8602,14 +8598,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8632,7 +8628,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8640,8 +8636,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8650,37 +8648,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8752,14 +8752,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8790,10 +8790,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8802,39 +8800,37 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8906,12 +8902,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8983,12 +8979,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9060,12 +9056,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9137,12 +9133,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9214,12 +9210,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9291,14 +9287,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9321,7 +9317,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9329,8 +9325,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="n">
-        <v>0</v>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9339,37 +9337,39 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9482,9 +9482,9 @@
       <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9591,14 +9591,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9630,11 +9630,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9664,14 +9664,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9702,8 +9702,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>0</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9712,39 +9714,41 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9767,7 +9771,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9775,10 +9779,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9787,39 +9789,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9887,14 +9887,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9925,8 +9925,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9935,39 +9937,41 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -9990,7 +9994,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9998,10 +10002,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -10010,39 +10012,37 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10187,14 +10187,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10225,10 +10225,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10237,39 +10235,37 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10341,12 +10337,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10418,12 +10414,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10495,12 +10491,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10572,12 +10568,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10649,12 +10645,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10726,12 +10722,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10803,12 +10799,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10880,14 +10876,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10910,7 +10906,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10918,8 +10914,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10928,39 +10926,41 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10991,8 +10991,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -11001,39 +11003,41 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11056,7 +11060,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11064,10 +11068,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11076,39 +11078,37 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11176,14 +11176,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11214,8 +11214,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>0</v>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -11224,37 +11226,39 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11322,14 +11326,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11352,7 +11356,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11360,10 +11364,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11372,41 +11374,39 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11437,10 +11437,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11449,39 +11447,37 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11553,12 +11549,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11630,12 +11626,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11707,12 +11703,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11784,12 +11780,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11861,12 +11857,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11938,12 +11934,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12015,12 +12011,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12092,12 +12088,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12169,12 +12165,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12246,12 +12242,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12323,14 +12319,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12353,7 +12349,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12361,8 +12357,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12371,39 +12369,41 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12434,8 +12434,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" s="2" t="n">
-        <v>0</v>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -12444,37 +12446,39 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12510,9 +12514,9 @@
       <c r="I159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12542,12 +12546,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12615,14 +12619,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12654,11 +12658,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12688,12 +12692,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12761,14 +12765,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -12791,7 +12795,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12799,10 +12803,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12811,39 +12813,37 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12879,9 +12879,9 @@
       <c r="I164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12911,12 +12911,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12988,14 +12988,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -13027,11 +13027,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13138,14 +13138,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-053</t>
@@ -13168,7 +13168,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -13176,10 +13176,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I168" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -13188,39 +13186,37 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13292,12 +13288,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13369,12 +13365,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13446,12 +13442,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13523,82 +13519,236 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
+++ b/saida_skus/SKU_BRINQ-053-KIT-PRAIA-8-PECAS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,8 +590,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>3</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -600,37 +602,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -655,7 +659,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -663,51 +667,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,10 +740,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -752,39 +750,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -809,7 +805,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,10 +813,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -829,39 +823,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -886,7 +878,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -894,51 +886,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,59 +951,55 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1049,11 +1033,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1083,12 +1067,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1113,7 +1097,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1121,10 +1105,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1133,39 +1115,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,7 +1170,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,10 +1178,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1210,39 +1188,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1314,12 +1290,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1391,12 +1367,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1444,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,7 +1474,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1506,8 +1482,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1516,37 +1494,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1618,12 +1598,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1659,9 +1639,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1691,12 +1671,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1768,12 +1748,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,55 +1778,59 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1871,7 +1855,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1879,8 +1863,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1889,37 +1875,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1944,7 +1932,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 38,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1952,8 +1940,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>7</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1962,37 +1952,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2017,7 +2009,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2025,47 +2017,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2090,7 +2086,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2098,10 +2094,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2110,39 +2104,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2167,7 +2159,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2175,8 +2167,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2185,37 +2179,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2251,9 +2247,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2283,12 +2279,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2360,12 +2356,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2393,17 +2389,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2433,12 +2429,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2463,7 +2459,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2471,10 +2467,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2483,39 +2477,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2540,7 +2532,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 38,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2549,24 +2541,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2583,12 +2575,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2613,7 +2605,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2621,51 +2613,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2690,7 +2678,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2698,47 +2686,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2763,7 +2755,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2771,10 +2763,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2783,39 +2773,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2849,7 +2837,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2883,12 +2871,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2960,12 +2948,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2990,7 +2978,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2998,51 +2986,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3114,12 +3098,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3153,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3187,12 +3171,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3264,12 +3248,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3294,7 +3278,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3302,51 +3286,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3418,12 +3398,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3448,7 +3428,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3456,10 +3436,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3468,39 +3446,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3572,12 +3548,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3649,12 +3625,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3726,12 +3702,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3756,7 +3732,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3764,10 +3740,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3776,39 +3750,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3880,12 +3852,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3957,12 +3929,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3987,7 +3959,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3995,8 +3967,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4005,37 +3979,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4107,12 +4083,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4184,12 +4160,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4261,12 +4237,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4338,12 +4314,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4415,12 +4391,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4492,12 +4468,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4569,12 +4545,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4599,7 +4575,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4607,10 +4583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4619,39 +4593,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4723,12 +4695,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4800,12 +4772,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4877,12 +4849,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4954,12 +4926,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5031,12 +5003,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5108,12 +5080,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5138,7 +5110,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5146,8 +5118,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5156,37 +5130,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5258,12 +5234,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5288,7 +5264,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5296,8 +5272,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5306,37 +5284,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5408,12 +5388,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5485,12 +5465,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5562,12 +5542,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5639,12 +5619,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5716,12 +5696,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5789,12 +5769,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5866,12 +5846,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5907,9 +5887,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5939,12 +5919,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,12 +5996,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6046,7 +6026,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6054,8 +6034,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6064,37 +6046,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6166,12 +6150,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6243,12 +6227,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6320,12 +6304,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6350,7 +6334,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6358,10 +6342,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6370,39 +6352,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6474,12 +6454,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6504,7 +6484,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6512,51 +6492,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6628,12 +6604,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6658,7 +6634,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6666,10 +6642,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6678,39 +6652,37 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6782,12 +6754,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6812,7 +6784,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6820,8 +6792,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6830,37 +6804,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6932,12 +6908,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6962,7 +6938,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6970,47 +6946,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7035,7 +7015,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -7043,8 +7023,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7053,37 +7035,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7108,7 +7092,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7116,8 +7100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>1</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7126,37 +7112,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7181,7 +7169,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7189,47 +7177,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7301,12 +7293,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7331,7 +7323,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7339,8 +7331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>1</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7349,37 +7343,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7404,7 +7400,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7412,10 +7408,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7424,39 +7418,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7528,12 +7520,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7558,7 +7550,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7566,51 +7558,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7635,7 +7623,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7643,10 +7631,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7655,39 +7641,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7721,7 +7705,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7755,12 +7739,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7785,7 +7769,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7793,51 +7777,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7862,7 +7842,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7870,8 +7850,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7880,37 +7862,39 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7935,7 +7919,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7943,10 +7927,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7955,39 +7937,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8059,12 +8039,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8136,12 +8116,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8213,12 +8193,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8290,12 +8270,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8320,7 +8300,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8328,10 +8308,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8340,39 +8318,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8444,12 +8420,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8474,7 +8450,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8482,10 +8458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8494,39 +8468,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8598,12 +8570,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8675,12 +8647,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8752,12 +8724,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8782,7 +8754,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8790,8 +8762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8800,37 +8774,39 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8902,12 +8878,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8979,12 +8955,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9056,12 +9032,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9133,12 +9109,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9210,12 +9186,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9287,12 +9263,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9364,12 +9340,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9394,7 +9370,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9402,10 +9378,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9414,39 +9388,37 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9471,7 +9443,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9479,8 +9451,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9489,37 +9463,39 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9591,12 +9567,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9621,7 +9597,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9629,47 +9605,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9741,12 +9721,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9771,7 +9751,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9779,8 +9759,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>1</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9789,37 +9771,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9844,7 +9828,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9852,8 +9836,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9862,37 +9848,39 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9964,12 +9952,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9994,7 +9982,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -10002,8 +9990,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -10012,37 +10002,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10110,12 +10102,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10187,12 +10179,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10228,9 +10220,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10260,12 +10252,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10337,12 +10329,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10367,7 +10359,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10375,10 +10367,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10387,39 +10377,37 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10444,7 +10432,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10452,10 +10440,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10464,39 +10450,37 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10568,12 +10552,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10598,7 +10582,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10606,10 +10590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10618,39 +10600,37 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10675,7 +10655,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10683,10 +10663,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10695,39 +10673,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10799,12 +10775,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10829,7 +10805,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10837,10 +10813,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10849,39 +10823,37 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10953,12 +10925,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11030,12 +11002,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11060,7 +11032,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11068,8 +11040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11078,37 +11052,39 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11133,7 +11109,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11141,8 +11117,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11151,37 +11129,39 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11253,12 +11233,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11283,7 +11263,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11291,8 +11271,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11301,37 +11283,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11356,7 +11340,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11364,8 +11348,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>0</v>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11374,37 +11360,39 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11429,7 +11417,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11437,8 +11425,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11447,37 +11437,39 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11549,12 +11541,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11626,12 +11618,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11656,7 +11648,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11664,10 +11656,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11676,39 +11666,37 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11733,7 +11721,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11741,10 +11729,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11753,39 +11739,37 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11857,12 +11841,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11887,7 +11871,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11895,10 +11879,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11907,39 +11889,37 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11964,7 +11944,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11972,10 +11952,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11984,39 +11962,37 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12041,7 +12017,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -12049,10 +12025,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -12061,39 +12035,37 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12165,12 +12137,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12242,12 +12214,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12319,12 +12291,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12396,12 +12368,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12473,12 +12445,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12503,7 +12475,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12511,8 +12483,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>0</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12521,37 +12495,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12576,7 +12552,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12584,8 +12560,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="2" t="n">
-        <v>0</v>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -12594,37 +12572,39 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12649,7 +12629,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12657,47 +12637,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12722,7 +12706,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12730,8 +12714,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="2" t="n">
-        <v>0</v>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -12740,37 +12726,39 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12795,7 +12783,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12803,8 +12791,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="n">
-        <v>1</v>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12813,37 +12803,39 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12868,7 +12860,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12876,8 +12868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="2" t="n">
-        <v>0</v>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12886,37 +12880,39 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12988,12 +12984,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13018,7 +13014,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -13026,47 +13022,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -13099,10 +13099,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -13111,39 +13109,37 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13177,7 +13173,7 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -13211,12 +13207,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13241,7 +13237,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13249,51 +13245,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13318,7 +13310,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -13326,10 +13318,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I170" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -13338,39 +13328,37 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13395,7 +13383,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13403,10 +13391,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13415,39 +13401,37 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13472,7 +13456,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13480,10 +13464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I172" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -13492,39 +13474,37 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13596,12 +13576,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13626,7 +13606,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13634,121 +13614,729 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>3065598308</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-053</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Kit praia 8 pecas</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3698489669</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-053</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Kit praia 8 pecas</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>3065598308</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 68,99</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,99</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>